--- a/레파토리목록.xlsx
+++ b/레파토리목록.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\80.슬기로운취미생활\집단적독백\Archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783F70F4-B9CE-4B86-B816-CA08BA181C41}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFCAD73-C29A-4320-A432-5BCC27C42A5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7395" xr2:uid="{995E4FF2-79AF-4A3D-AB88-494435202B7B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7395" activeTab="1" xr2:uid="{995E4FF2-79AF-4A3D-AB88-494435202B7B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="공연별레파토리" sheetId="1" r:id="rId1"/>
+    <sheet name="곡설명" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="148">
   <si>
     <t xml:space="preserve">10. (합주) 알함브라 궁전의 추억 </t>
   </si>
@@ -126,10 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>전체</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Gently, by your side(곁에 있어도 될까요)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -234,13 +231,275 @@
   <si>
     <t>베키짱, 베리짱, 쿠르짱, 로나짱, 택건뷰짱, 유니뀨짱</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duo in G</t>
+  </si>
+  <si>
+    <t>장르</t>
+  </si>
+  <si>
+    <t>Jazz</t>
+  </si>
+  <si>
+    <t>Pop</t>
+  </si>
+  <si>
+    <t>한동준</t>
+  </si>
+  <si>
+    <t>Classical</t>
+  </si>
+  <si>
+    <t>송창식</t>
+  </si>
+  <si>
+    <t>Paul Anka</t>
+  </si>
+  <si>
+    <t>Michael Hoppé</t>
+  </si>
+  <si>
+    <t>Stanley Myers</t>
+  </si>
+  <si>
+    <t>Máximo Diego Pujol</t>
+  </si>
+  <si>
+    <t>Recuerdos de la Alhambra</t>
+  </si>
+  <si>
+    <t>Roland Dyens</t>
+  </si>
+  <si>
+    <t>김광석</t>
+  </si>
+  <si>
+    <t>Luiz Bonfá</t>
+  </si>
+  <si>
+    <t>예민</t>
+  </si>
+  <si>
+    <t>조용필, 심수봉, 최백호</t>
+  </si>
+  <si>
+    <t>작곡가(가수)</t>
+  </si>
+  <si>
+    <t>곡명</t>
+  </si>
+  <si>
+    <t>Fly Me to the Moon</t>
+  </si>
+  <si>
+    <t>Bart Howard (Frank Sinatra)</t>
+  </si>
+  <si>
+    <t>Put Your Head on My Shoulder</t>
+  </si>
+  <si>
+    <t>Beloved</t>
+  </si>
+  <si>
+    <t>New Age</t>
+  </si>
+  <si>
+    <t>Cavatina</t>
+  </si>
+  <si>
+    <t>OST / Classical</t>
+  </si>
+  <si>
+    <t>Misty</t>
+  </si>
+  <si>
+    <t>Erroll Garner</t>
+  </si>
+  <si>
+    <t>너를 사랑해</t>
+  </si>
+  <si>
+    <t>K-pop</t>
+  </si>
+  <si>
+    <t>Bésame Mucho</t>
+  </si>
+  <si>
+    <t>Consuelo Velázquez</t>
+  </si>
+  <si>
+    <t>Latin / Bolero</t>
+  </si>
+  <si>
+    <t>Autumn Leaves</t>
+  </si>
+  <si>
+    <t>Joseph Kosma</t>
+  </si>
+  <si>
+    <t>Preludio Tristón</t>
+  </si>
+  <si>
+    <t>사랑 그 쓸쓸함에 대하여</t>
+  </si>
+  <si>
+    <t>이병우 (양희은)</t>
+  </si>
+  <si>
+    <t>K-pop / Ballad</t>
+  </si>
+  <si>
+    <t>Francisco Tárrega</t>
+  </si>
+  <si>
+    <t>곁에 있어도 될까 (Gently, by Your Side)</t>
+  </si>
+  <si>
+    <t>시와 (Siwa)</t>
+  </si>
+  <si>
+    <t>K-pop / Indie Folk</t>
+  </si>
+  <si>
+    <t>Silvestre Fonseca</t>
+  </si>
+  <si>
+    <t>Romance No. 1</t>
+  </si>
+  <si>
+    <t>K-pop / Folk</t>
+  </si>
+  <si>
+    <t>이봉조 (정훈희)</t>
+  </si>
+  <si>
+    <t>OST / Bossa Nova</t>
+  </si>
+  <si>
+    <t>Canzone d'Amore</t>
+  </si>
+  <si>
+    <t>산골 소년의 사랑이야기</t>
+  </si>
+  <si>
+    <t>Trot Medley (돌아와요 부산항에, 사랑밖엔 난 몰라, 낭만에 대하여)</t>
+  </si>
+  <si>
+    <t>우리는</t>
+  </si>
+  <si>
+    <t>Maria Linnemann</t>
+  </si>
+  <si>
+    <t>Ferdinando Carulli</t>
+  </si>
+  <si>
+    <t>Francis Kleynjans</t>
+  </si>
+  <si>
+    <t>Anonymous (Francis Goya)</t>
+  </si>
+  <si>
+    <t>K-pop / Trot</t>
+  </si>
+  <si>
+    <t>고덕우갤러리(2025)</t>
+  </si>
+  <si>
+    <t>꿈꾸는공작소(2025)</t>
+  </si>
+  <si>
+    <t>고덕우갤러리(2026)</t>
+  </si>
+  <si>
+    <t>함께</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곡설명</t>
+  </si>
+  <si>
+    <t>이탈리아 기타 작곡가 카룰리의 2중주곡. 두 대의 기타가 선율과 반주를 주고받으며 밝고 경쾌한 조화를 이룬다.</t>
+  </si>
+  <si>
+    <t>달까지 날아가고 싶다는 낭만적인 사랑의 감정을 노래한 재즈 스탠더드. 프랭크 시나트라의 스윙 버전으로 널리 사랑받았다.</t>
+  </si>
+  <si>
+    <t>1959년 발표된 폴 앵카의 대표적인 러브송. 사랑하는 사람에게 어깨를 내어주고 가까이 머물기를 바라는 따뜻한 노래.</t>
+  </si>
+  <si>
+    <t>마이클 호페의 서정적인 뉴에이지 작품. 2000년 영국 왕대비의 100세 생일을 기념한 헌정 앨범에 수록된 곡으로, 부드럽고 애틋한 선율이 특징이다.</t>
+  </si>
+  <si>
+    <t>영화 《디어 헌터》(1978)의 주제곡으로 유명해진 클래식 기타 명곡. 존 윌리엄스의 연주로 널리 알려졌으며 아름답고 애잔한 선율이 깊은 여운을 남긴다.</t>
+  </si>
+  <si>
+    <t>재즈 피아니스트 에롤 가너가 1954년 작곡한 재즈 발라드. 사랑에 빠진 사람의 몽환적이고 설레는 감정을 표현한 재즈 스탠더드.</t>
+  </si>
+  <si>
+    <t>사랑하는 사람에게 전하는 진솔하고 따뜻한 고백을 담은 곡. 소박한 가사와 아름다운 선율로 오랫동안 사랑받아 온 한국의 대표적인 사랑 노래.</t>
+  </si>
+  <si>
+    <t>'나에게 뜨겁게 키스해 주세요'라는 뜻의 멕시코 볼레로 명곡. 사랑하는 사람과 헤어질지도 모른다는 두려움과 간절한 사랑을 표현한다.</t>
+  </si>
+  <si>
+    <t>프랑스 샹송 《Les Feuilles mortes》(고엽)에서 출발한 재즈 스탠더드. 낙엽이 지는 가을 풍경에 지나간 사랑의 그리움을 담은 곡.</t>
+  </si>
+  <si>
+    <t>아르헨티나 기타 작곡가 푸홀의 작품. 밀롱가 특유의 리듬과 쓸쓸한 선율이 어우러져 남미 음악의 서정성을 느낄 수 있다.</t>
+  </si>
+  <si>
+    <t>사랑이 지나간 자리에 남는 외로움과 쓸쓸함을 담담하게 표현한 노래. 양희은의 깊이 있는 목소리와 이병우의 서정적인 작곡이 돋보인다.</t>
+  </si>
+  <si>
+    <t>Romance D´amour (Spanish Romance)</t>
+  </si>
+  <si>
+    <t>'사랑의 로망스'로 알려진 스페인풍 기타 명곡. 영화 《금지된 장난》을 통해 널리 알려졌으며, 애절하고 낭만적인 아르페지오 선율이 특징이다.</t>
+  </si>
+  <si>
+    <t>'알함브라 궁전의 추억'이라는 뜻의 클래식 기타 대표작. 빠르게 반복되는 트레몰로 기법으로 아련하고 환상적인 선율을 만들어 낸다.</t>
+  </si>
+  <si>
+    <t>인디 포크 싱어송라이터 시와의 노래. 누군가의 곁에 조심스럽게 머물고 싶은 마음을 소박한 목소리와 따뜻한 선율로 전한다.</t>
+  </si>
+  <si>
+    <t>프랑스 기타리스트 롤랑 디앙의 독창적인 왈츠곡. 공연장의 대기실에서 조금씩 작곡한 작품으로, 경쾌한 왈츠 리듬과 재치 있는 음악적 표현이 특징이다.</t>
+  </si>
+  <si>
+    <t>'어느 밤의 선율'이라는 뜻의 포르투갈 기타 작품. 밤의 고요함을 연상시키는 부드럽고 서정적인 선율이 매력적인 곡.</t>
+  </si>
+  <si>
+    <t>프랑스 기타 작곡가 클레냥스의 기타 2중주 작품(Op.100). 두 대의 기타가 부드러운 선율을 주고받으며 낭만적인 분위기를 만들어 낸다.</t>
+  </si>
+  <si>
+    <t>떠나간 사랑을 잊으려 하지만 지울 수 없는 그리움을 노래한 김광석의 대표곡. 절제된 감정과 담담한 가사가 깊은 울림을 전한다.</t>
+  </si>
+  <si>
+    <t>1967년 정훈희의 데뷔곡. 안개처럼 불확실하고 쓸쓸한 사랑의 감정을 몽환적인 분위기와 호소력 있는 목소리로 표현한 명곡.</t>
+  </si>
+  <si>
+    <t>브라질 영화 《흑인 오르페》(1959)의 대표적인 삽입곡. '카니발의 아침'이라는 뜻으로, 브라질 음악 특유의 리듬에 서정적이고 애틋한 선율을 담았다.</t>
+  </si>
+  <si>
+    <t>'사랑의 노래'라는 뜻의 클래식 기타 소품. 노래하듯 자연스럽게 흐르는 선율과 섬세한 화성이 따뜻하고 낭만적인 분위기를 자아낸다.</t>
+  </si>
+  <si>
+    <t>순수한 산골 소년의 사랑과 자연의 아름다움을 동화처럼 그려 낸 노래. 맑고 서정적인 멜로디가 어린 시절의 추억과 순수함을 떠올리게 한다.</t>
+  </si>
+  <si>
+    <t>그리운 이를 기다리는 마음, 사랑에 대한 헌신, 지나간 청춘에 대한 향수를 담은 세 곡의 메들리. 한국 대중가요 특유의 정서와 흥겨움을 함께 느낄 수 있다.</t>
+  </si>
+  <si>
+    <t>서로 다른 사람들이 함께 살아가는 삶과 인연의 의미를 노래한 송창식의 대표곡. 힘 있는 선율과 철학적인 가사가 어우러져 깊은 울림을 전한다.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,13 +515,28 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -279,9 +553,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,49 +902,55 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
         <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
         <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -672,134 +958,167 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -807,123 +1126,153 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="D24" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="D26" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
@@ -931,112 +1280,142 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="D32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="D34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
         <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="D35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="D36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
         <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1044,4 +1423,371 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCFD113-907E-4C60-A217-B19A22E4CDE9}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.125" customWidth="1"/>
+    <col min="2" max="2" width="26.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/레파토리목록.xlsx
+++ b/레파토리목록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\80.슬기로운취미생활\집단적독백\Archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFCAD73-C29A-4320-A432-5BCC27C42A5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A12FBF6-4837-429C-A7B6-E13FADA53CBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7395" activeTab="1" xr2:uid="{995E4FF2-79AF-4A3D-AB88-494435202B7B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7395" xr2:uid="{995E4FF2-79AF-4A3D-AB88-494435202B7B}"/>
   </bookViews>
   <sheets>
     <sheet name="공연별레파토리" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="176">
   <si>
     <t xml:space="preserve">10. (합주) 알함브라 궁전의 추억 </t>
   </si>
@@ -172,24 +172,12 @@
     <t>5중주, 베키짱</t>
   </si>
   <si>
-    <t>민철, 베키짱</t>
-  </si>
-  <si>
     <t>베리짱, 쿠르짱</t>
   </si>
   <si>
-    <t>베리짱,쿠르짱,금주</t>
-  </si>
-  <si>
     <t>베키짱, 로나짱</t>
   </si>
   <si>
-    <t xml:space="preserve"> 로나짱</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 민철, 로나짱</t>
-  </si>
-  <si>
     <t>로나짱</t>
   </si>
   <si>
@@ -202,15 +190,6 @@
     <t>유니뀨짱</t>
   </si>
   <si>
-    <t xml:space="preserve"> 유니뀨짱 베키짱</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 로나짱, 유니뀨짱</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 유니뀨짱</t>
-  </si>
-  <si>
     <t>베키짱, 유니뀨짱</t>
   </si>
   <si>
@@ -226,9 +205,6 @@
     <t>베리짱, 유니뀨짱</t>
   </si>
   <si>
-    <t>베리짱, 쿠르짱, 로나짱,  유니뀨짱, 금주</t>
-  </si>
-  <si>
     <t>베키짱, 베리짱, 쿠르짱, 로나짱, 택건뷰짱, 유니뀨짱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -493,6 +469,126 @@
   </si>
   <si>
     <t>서로 다른 사람들이 함께 살아가는 삶과 인연의 의미를 노래한 송창식의 대표곡. 힘 있는 선율과 철학적인 가사가 어우러져 깊은 울림을 전한다.</t>
+  </si>
+  <si>
+    <t>No 5.</t>
+  </si>
+  <si>
+    <t>No 5.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매니저, 베키짱</t>
+  </si>
+  <si>
+    <t>유니뀨짱, 베키짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로나짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로나짱, 유니뀨짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유니뀨짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매니저, 로나짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유니뀨짱,베키짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Siesta in Granada</t>
+  </si>
+  <si>
+    <t>생활성가 「꽃」</t>
+  </si>
+  <si>
+    <t>베리짱,쿠르짱,세뉴짱</t>
+  </si>
+  <si>
+    <t>베리짱, 쿠르짱, 로나짱,  유니뀨짱, 세뉴짱</t>
+  </si>
+  <si>
+    <t>예수성심전교수녀회(2026)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아베 마리아(Ave Maria)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화개고인래(花開故人來) — 중국 기악곡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화개고인래 (花開故人來)</t>
+  </si>
+  <si>
+    <t>차이쥔리(蔡军礼) 작곡</t>
+  </si>
+  <si>
+    <t>Chinese Traditional / Instrumental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'꽃이 피니 옛 벗이 찾아온다'는 뜻으로, 꽃이 피는 계절의 재회와 그리움을 표현한 중국 기악곡. 중국 전통 대나무 피리인 죽적(디즈)의 서정적인 선율이 특징이다. </t>
+  </si>
+  <si>
+    <t>아베 마리아 (Ave Maria)</t>
+  </si>
+  <si>
+    <t>샤를 구노(Charles Gounod) 작곡 / J. S. 바흐 원곡</t>
+  </si>
+  <si>
+    <t>Classical / Sacred Music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바흐의 《평균율 클라비어곡집》 제1권 전주곡 1번 위에 구노가 아름다운 선율을 덧붙인 작품. 성모 마리아에게 바치는 기도의 경건함과 평온함을 담은 대표적인 종교음악이다. </t>
+  </si>
+  <si>
+    <t>엘 카디스(El Cadiz) 작곡*</t>
+  </si>
+  <si>
+    <t>Spanish Guitar / Instrumental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'그라나다에서의 낮잠'이라는 뜻으로, 스페인 남부의 따뜻한 햇살과 여유로운 오후를 연상시키는 기타 기악곡. 스페인 특유의 정취를 어쿠스틱 기타 선율로 표현한다. </t>
+  </si>
+  <si>
+    <t>현덕 프란치스코 작사·작곡</t>
+  </si>
+  <si>
+    <t>Catholic CCM / 생활성가</t>
+  </si>
+  <si>
+    <t>1997년에 만들어진 생활성가로, 순교자들의 믿음과 삶을 한 송이 꽃에 비유한 곡. 어려움 속에서도 신앙을 지키며 세상에 사랑을 전하는 모습을 서정적인 선율에 담았다</t>
+  </si>
+  <si>
+    <t>유니뀨짱, 로나짱</t>
+  </si>
+  <si>
+    <t>베키짱, 민철</t>
+  </si>
+  <si>
+    <t>베리짱, 세뉴짱, 쿠르짱</t>
+  </si>
+  <si>
+    <t>베리짱, 세뉴짱, 쿠르짱, 로나짱, 유니뀨짱</t>
+  </si>
+  <si>
+    <t>수녀님1(플루트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수녀님2, 베리짱, 유니뀨짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -877,13 +973,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A71186-45DA-4505-9EEC-E4A228C420B0}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="54.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -908,7 +1004,7 @@
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
         <v>36</v>
@@ -922,7 +1018,7 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
         <v>36</v>
@@ -936,7 +1032,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
         <v>36</v>
@@ -950,7 +1046,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -964,7 +1060,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -978,10 +1074,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -992,10 +1088,10 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1006,10 +1102,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1020,10 +1116,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1034,10 +1130,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1048,10 +1144,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1062,10 +1158,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1076,10 +1172,10 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1090,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1104,10 +1200,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1118,7 +1214,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -1132,7 +1228,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -1146,10 +1242,10 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1160,10 +1256,10 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1174,10 +1270,10 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1188,10 +1284,10 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1202,10 +1298,10 @@
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1216,10 +1312,10 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1230,10 +1326,10 @@
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1244,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1261,7 +1357,7 @@
         <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1272,7 +1368,7 @@
         <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
@@ -1286,7 +1382,7 @@
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
@@ -1300,10 +1396,10 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1314,10 +1410,10 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1328,10 +1424,10 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1342,10 +1438,10 @@
         <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1356,10 +1452,10 @@
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1370,10 +1466,10 @@
         <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1384,10 +1480,10 @@
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1398,10 +1494,10 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1412,10 +1508,164 @@
         <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D41" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D43" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D45" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D47" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -1427,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCFD113-907E-4C60-A217-B19A22E4CDE9}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1438,212 +1688,212 @@
   <sheetData>
     <row r="1" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1651,13 +1901,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1665,27 +1915,27 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1693,13 +1943,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1707,13 +1957,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1721,69 +1971,125 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/레파토리목록.xlsx
+++ b/레파토리목록.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\80.슬기로운취미생활\집단적독백\Archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A12FBF6-4837-429C-A7B6-E13FADA53CBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C336271B-A089-45E7-AAD9-B1468453B4B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7395" xr2:uid="{995E4FF2-79AF-4A3D-AB88-494435202B7B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7395" activeTab="1" xr2:uid="{995E4FF2-79AF-4A3D-AB88-494435202B7B}"/>
   </bookViews>
   <sheets>
     <sheet name="공연별레파토리" sheetId="1" r:id="rId1"/>
-    <sheet name="곡설명" sheetId="3" r:id="rId2"/>
+    <sheet name="파일럿공연" sheetId="4" r:id="rId2"/>
+    <sheet name="곡설명" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="200">
   <si>
     <t xml:space="preserve">10. (합주) 알함브라 궁전의 추억 </t>
   </si>
@@ -181,9 +182,6 @@
     <t>로나짱</t>
   </si>
   <si>
-    <t>베키짱(노래), 베리짱, 쿠르짱, 로나짱, 택원, 유니뀨짱</t>
-  </si>
-  <si>
     <t>베키짱(노래), 베리짱, 쿠르짱, 로나짱(노래), 택원, 유니뀨짱</t>
   </si>
   <si>
@@ -574,9 +572,6 @@
     <t>유니뀨짱, 로나짱</t>
   </si>
   <si>
-    <t>베키짱, 민철</t>
-  </si>
-  <si>
     <t>베리짱, 세뉴짱, 쿠르짱</t>
   </si>
   <si>
@@ -588,6 +583,107 @@
   </si>
   <si>
     <t>수녀님2, 베리짱, 유니뀨짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결혼축가1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BIFC몰 루이하우스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">01. (중주) 05.Besame mucho </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.12.7.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결혼축가2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로나짱(기타), 유니뀨짱(기타)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연주자(역할)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베키짱(노래), 베리짱(기타), 쿠르짱(기타), 로나짱(기타), 유니뀨짱(기타)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노을음악회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01.잊어야 한다는 마음으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로나짱(기타), 매니저(하모니카)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베키짱, 매니저</t>
+  </si>
+  <si>
+    <t>2025.12.27.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜드모먼트 웨딩홀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.10.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>온종합병원(ONN닥터TV홀)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.10.18.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.11.22.</t>
+  </si>
+  <si>
+    <t>2025.11.22.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.11.08.</t>
+  </si>
+  <si>
+    <t>2026.11.08.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.01.10.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베키짱(노래), 로나짱(기타,멜로디언),유니뀨짱(기타)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베키짱(노래), 베리짱, 쿠르짱, 로나짱(멜로디언), 택원, 유니뀨짱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -649,7 +745,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -658,6 +754,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -973,30 +1078,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A71186-45DA-4505-9EEC-E4A228C420B0}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="54.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.625" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -1004,13 +1113,16 @@
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1018,13 +1130,16 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="D3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1032,13 +1147,16 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1051,8 +1169,11 @@
       <c r="D5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -1065,8 +1186,11 @@
       <c r="D6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1074,13 +1198,16 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1088,13 +1215,16 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1102,13 +1232,16 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1116,13 +1249,16 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1130,13 +1266,16 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1144,13 +1283,16 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1158,13 +1300,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1172,13 +1317,16 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1186,13 +1334,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1200,13 +1351,16 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="E16" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1219,8 +1373,11 @@
       <c r="D17" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1233,8 +1390,11 @@
       <c r="D18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1242,13 +1402,16 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E19" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -1256,13 +1419,16 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1270,13 +1436,16 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1284,13 +1453,16 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -1298,13 +1470,16 @@
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1312,13 +1487,16 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -1326,13 +1504,16 @@
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1340,13 +1521,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1357,10 +1541,13 @@
         <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="E27" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -1368,13 +1555,16 @@
         <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1382,13 +1572,16 @@
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1399,10 +1592,13 @@
         <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1410,13 +1606,16 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -1424,13 +1623,16 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1438,13 +1640,16 @@
         <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1452,13 +1657,16 @@
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E34" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -1466,13 +1674,16 @@
         <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E35" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -1483,10 +1694,13 @@
         <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E36" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -1494,13 +1708,16 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E37" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -1508,29 +1725,35 @@
         <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="E39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>16</v>
@@ -1539,133 +1762,163 @@
         <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="E40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="E41" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
+        <v>152</v>
+      </c>
+      <c r="E42" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" t="s">
+        <v>152</v>
+      </c>
+      <c r="E43" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>140</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D43" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="C44" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D44" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="E44" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D45" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="E45" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D46" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="E46" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D47" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="E47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="E48" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" t="s">
         <v>152</v>
       </c>
-      <c r="D49" t="s">
-        <v>153</v>
+      <c r="E49" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -1676,6 +1929,127 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1479848-A8C0-47AB-B9F2-29D81381F883}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="30.625" customWidth="1"/>
+    <col min="3" max="3" width="49.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCFD113-907E-4C60-A217-B19A22E4CDE9}">
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1688,212 +2062,212 @@
   <sheetData>
     <row r="1" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1901,13 +2275,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1915,27 +2289,27 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1943,13 +2317,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1957,13 +2331,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1971,125 +2345,125 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/레파토리목록.xlsx
+++ b/레파토리목록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\80.슬기로운취미생활\집단적독백\Archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C336271B-A089-45E7-AAD9-B1468453B4B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F80EBB8-1070-42BD-B114-C40ABC573EE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7395" activeTab="1" xr2:uid="{995E4FF2-79AF-4A3D-AB88-494435202B7B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7395" activeTab="2" xr2:uid="{995E4FF2-79AF-4A3D-AB88-494435202B7B}"/>
   </bookViews>
   <sheets>
     <sheet name="공연별레파토리" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="207">
   <si>
     <t xml:space="preserve">10. (합주) 알함브라 궁전의 추억 </t>
   </si>
@@ -506,9 +506,6 @@
     <t>Siesta in Granada</t>
   </si>
   <si>
-    <t>생활성가 「꽃」</t>
-  </si>
-  <si>
     <t>베리짱,쿠르짱,세뉴짱</t>
   </si>
   <si>
@@ -519,10 +516,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아베 마리아(Ave Maria)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>화개고인래(花開故人來) — 중국 기악곡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -684,6 +677,42 @@
   </si>
   <si>
     <t>베키짱(노래), 베리짱, 쿠르짱, 로나짱(멜로디언), 택원, 유니뀨짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천 개의 바람이 되어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수녀님1(플루트), 수녀님2(기타)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「꽃」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베리짱, 세뉴짱, 쿠르짱, 로나짱, 유니뀨짱, 수녀님들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베리짱, 베키짱, 쿠르짱, 로나짱,  유니뀨짱, 세뉴짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꽃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아라이 만(임형주)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Popera / Crossover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영미권의 추모시에 곡을 붙인 작품. 세상을 떠난 사랑하는 사람이 바람과 햇살이 되어 우리 곁에 머문다는 메시지를 담고 있으며, 이별의 슬픔을 따뜻한 위로와 희망으로 승화시킨 서정적인 곡.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1102,7 +1131,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1119,7 +1148,7 @@
         <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,13 +1159,13 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D3" t="s">
         <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1153,7 +1182,7 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1170,7 +1199,7 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1187,7 +1216,7 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1204,7 +1233,7 @@
         <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1221,7 +1250,7 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1238,7 +1267,7 @@
         <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1255,7 +1284,7 @@
         <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1272,7 +1301,7 @@
         <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1289,7 +1318,7 @@
         <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1306,7 +1335,7 @@
         <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1323,7 +1352,7 @@
         <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1340,7 +1369,7 @@
         <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1357,7 +1386,7 @@
         <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1374,7 +1403,7 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1391,7 +1420,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1408,7 +1437,7 @@
         <v>110</v>
       </c>
       <c r="E19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1425,7 +1454,7 @@
         <v>110</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1442,7 +1471,7 @@
         <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1459,7 +1488,7 @@
         <v>110</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1476,7 +1505,7 @@
         <v>110</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1493,7 +1522,7 @@
         <v>110</v>
       </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1510,7 +1539,7 @@
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1527,7 +1556,7 @@
         <v>110</v>
       </c>
       <c r="E26" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1544,7 +1573,7 @@
         <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1561,7 +1590,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1578,7 +1607,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1595,7 +1624,7 @@
         <v>111</v>
       </c>
       <c r="E30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1612,7 +1641,7 @@
         <v>111</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1629,7 +1658,7 @@
         <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1646,7 +1675,7 @@
         <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1657,13 +1686,13 @@
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
         <v>111</v>
       </c>
       <c r="E34" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1680,7 +1709,7 @@
         <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1697,7 +1726,7 @@
         <v>111</v>
       </c>
       <c r="E36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1708,13 +1737,13 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
         <v>111</v>
       </c>
       <c r="E37" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1731,7 +1760,7 @@
         <v>111</v>
       </c>
       <c r="E38" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1745,10 +1774,10 @@
         <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E39" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1762,10 +1791,10 @@
         <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1773,16 +1802,16 @@
         <v>139</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>17</v>
+        <v>198</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E41" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1790,16 +1819,16 @@
         <v>139</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="D42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1807,16 +1836,16 @@
         <v>139</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E43" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1824,16 +1853,16 @@
         <v>139</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E44" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1844,13 +1873,13 @@
         <v>148</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E45" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1861,13 +1890,13 @@
         <v>20</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E46" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1878,13 +1907,13 @@
         <v>21</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1892,16 +1921,16 @@
         <v>139</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E48" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1912,13 +1941,13 @@
         <v>22</v>
       </c>
       <c r="C49" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" t="s">
         <v>151</v>
       </c>
-      <c r="D49" t="s">
-        <v>152</v>
-      </c>
       <c r="E49" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1948,98 +1977,98 @@
         <v>10</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" t="s">
         <v>174</v>
       </c>
-      <c r="B2" t="s">
-        <v>176</v>
-      </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2051,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCFD113-907E-4C60-A217-B19A22E4CDE9}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -2412,30 +2441,30 @@
     </row>
     <row r="26" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -2443,27 +2472,41 @@
         <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>168</v>
+    </row>
+    <row r="30" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
